--- a/docs/downloads/04/tbl_other_act_all_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_alaotra_ambatoharanana.xlsx
@@ -387,12 +387,6 @@
           <t>Commerçant, épicier, vendeur - Mpivarotra</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Elève, Etudiant- Mpianatra</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +441,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -490,12 +466,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -508,12 +478,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -526,12 +490,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -544,12 +502,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -562,12 +514,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -580,12 +526,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,12 +538,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -634,12 +568,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +580,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +592,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -706,12 +622,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -760,12 +670,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -796,12 +700,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +712,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -850,12 +742,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -868,12 +754,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -922,12 +802,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -958,12 +832,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1012,12 +880,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1030,12 +892,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="D38">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1048,12 +904,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C39">
-        <v>3</v>
-      </c>
-      <c r="D39">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1066,12 +916,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-      <c r="D40">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1101,12 +945,6 @@
         <is>
           <t>Taxi-bicyclette</t>
         </is>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
       </c>
     </row>
     <row r="43">
